--- a/artfynd/A 5911-2022 artfynd.xlsx
+++ b/artfynd/A 5911-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5911-2022 artfynd.xlsx
+++ b/artfynd/A 5911-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105594080</v>
+        <v>594330</v>
       </c>
       <c r="B2" t="n">
-        <v>102161</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,21 +703,25 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Floraväktarlokal 113P5, Ög</t>
+          <t>Groveda NNO, 450 m, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541655.8859105787</v>
+        <v>541567</v>
       </c>
       <c r="R2" t="n">
-        <v>6448153.603691173</v>
+        <v>6448038</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -734,7 +733,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Kinda</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -744,36 +743,31 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Vårdnäs</t>
+          <t>Tjärstad</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>E-Kin-0622</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-07-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2007-09-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-07-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2007-09-14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>inga exemplar funna på dellokal 113P5 inom floraväkteriet. Lokalen bedöms alltför igenvuxen för spindelört.</t>
+          <t>Koordinater: 1494213/6449792 113P2</t>
         </is>
       </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
@@ -785,27 +779,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gunnar Ölfvingsson</t>
+          <t>E-län Floraväktarna</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunnar Ölfvingsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Carina Greiff-andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62054050</v>
+        <v>6840837</v>
       </c>
       <c r="B3" t="n">
-        <v>102161</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>105117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,24 +823,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Groveda NNO, 550 m, Ög</t>
+          <t>Västerängen, 465 m NNO Groveda, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541640.3547221</v>
+        <v>541567</v>
       </c>
       <c r="R3" t="n">
-        <v>6448122.846649425</v>
+        <v>6448053</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,7 +854,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Kinda</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -866,65 +864,166 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Vårdnäs</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>E-Lin-0866</t>
+          <t>Tjärstad</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-08-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-06-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-08-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-06-25</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>113P5</t>
+          <t>hårt betat, avslitna och brutna stänglar. Medobservatör Janne Andersson</t>
         </is>
       </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134218045</v>
+      </c>
+      <c r="B4" t="n">
+        <v>9414</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>101246</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ekoxe</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lucanus cervus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Solhagen, Gärdala 1, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>541458</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6448049</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Levande hona.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Monika Sunhede</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Leif Andersson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Monika Sunhede</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5911-2022 artfynd.xlsx
+++ b/artfynd/A 5911-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -792,6 +797,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/594330</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6840837</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1024,8 +1039,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134218045</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>